--- a/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
+++ b/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Emerson\SolaHD\SDU-DC-UPS-EIP\PCBA\TesterSpecific\FRU PROGRAMMING TOOLKIT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EA45878D-3E51-48B3-9E78-E57D4D0819C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{308A4A56-7819-444D-B8C5-080C05EED5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9538C7C6-F33D-4746-B93C-9BE93615E927}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9538C7C6-F33D-4746-B93C-9BE93615E927}"/>
   </bookViews>
   <sheets>
     <sheet name="FRU Array" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t>FRU Information</t>
   </si>
@@ -244,7 +244,13 @@
     <t>0624</t>
   </si>
   <si>
+    <t>02C0</t>
+  </si>
+  <si>
     <t>0600</t>
+  </si>
+  <si>
+    <t>FF</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1579,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1627,6 +1633,12 @@
     <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>40</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="D36">
         <v>128</v>

--- a/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
+++ b/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Emerson\SolaHD\SDU-DC-UPS-EIP\PCBA\TesterSpecific\FRU PROGRAMMING TOOLKIT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{308A4A56-7819-444D-B8C5-080C05EED5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D3BE0B03-20FE-4720-96FB-43A6447BBFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9538C7C6-F33D-4746-B93C-9BE93615E927}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>FRU Information</t>
   </si>
@@ -142,9 +142,6 @@
     <t>Flyback TRF Temp C.C 1</t>
   </si>
   <si>
-    <t>Event Data</t>
-  </si>
-  <si>
     <t>0022</t>
   </si>
   <si>
@@ -251,6 +248,12 @@
   </si>
   <si>
     <t>FF</t>
+  </si>
+  <si>
+    <t>=B36+0008</t>
+  </si>
+  <si>
+    <t>Event Data 1</t>
   </si>
 </sst>
 </file>
@@ -1215,10 +1218,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D6">
         <v>128</v>
@@ -1229,10 +1232,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D7">
         <v>32</v>
@@ -1243,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -1257,10 +1260,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>128</v>
@@ -1271,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2">
         <v>4141</v>
@@ -1285,10 +1288,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D11">
         <v>128</v>
@@ -1299,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>128</v>
@@ -1327,7 +1330,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -1341,7 +1344,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2">
         <v>32</v>
@@ -1355,7 +1358,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2">
         <v>14</v>
@@ -1369,7 +1372,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2">
         <v>78</v>
@@ -1383,10 +1386,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="D18">
         <v>128</v>
@@ -1397,10 +1400,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19">
         <v>128</v>
@@ -1411,7 +1414,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -1425,7 +1428,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -1439,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1453,7 +1456,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -1467,7 +1470,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -1481,7 +1484,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -1495,7 +1498,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1509,7 +1512,7 @@
         <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -1523,7 +1526,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1537,7 +1540,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1551,7 +1554,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1565,7 +1568,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1579,7 +1582,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1593,7 +1596,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1607,7 +1610,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1621,7 +1624,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1632,16 +1635,21 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="B37" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="D36">
-        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:4">

--- a/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
+++ b/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Emerson\SolaHD\SDU-DC-UPS-EIP\PCBA\TesterSpecific\FRU PROGRAMMING TOOLKIT\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D3BE0B03-20FE-4720-96FB-43A6447BBFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9538C7C6-F33D-4746-B93C-9BE93615E927}"/>
+    <workbookView windowWidth="14400" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="FRU Array" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
   <si>
     <t>FRU Information</t>
   </si>
@@ -37,257 +44,311 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>EEPROM Major Version</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>EEPROM Minor Version</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>nInitialized</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>nWriteProtect</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
     <t>Product Name</t>
   </si>
   <si>
+    <t>0022</t>
+  </si>
+  <si>
+    <t>5344552032303234422D454950</t>
+  </si>
+  <si>
     <t>Serial Number</t>
   </si>
   <si>
+    <t>0032</t>
+  </si>
+  <si>
+    <t>A9858001</t>
+  </si>
+  <si>
     <t>Manufacturing Info</t>
   </si>
   <si>
+    <t>003C</t>
+  </si>
+  <si>
+    <t>Manufacturer Name</t>
+  </si>
+  <si>
+    <t>0046</t>
+  </si>
+  <si>
+    <t>534455203230</t>
+  </si>
+  <si>
     <t>Model Revision</t>
   </si>
   <si>
+    <t>0056</t>
+  </si>
+  <si>
+    <t>FW Major Rev</t>
+  </si>
+  <si>
+    <t>0058</t>
+  </si>
+  <si>
+    <t>MCU FW Minor Rev</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>Lifetime Turn On Time</t>
+  </si>
+  <si>
     <t>00A0</t>
   </si>
   <si>
-    <t>EEPROM Major Version</t>
-  </si>
-  <si>
-    <t>EEPROM Minor Version</t>
-  </si>
-  <si>
-    <t>nInitialized</t>
-  </si>
-  <si>
-    <t>nWriteProtect</t>
-  </si>
-  <si>
-    <t>Manufacturer Name</t>
-  </si>
-  <si>
-    <t>FW Major Rev</t>
-  </si>
-  <si>
-    <t>MCU FW Minor Rev</t>
-  </si>
-  <si>
-    <t>Lifetime Turn On Time</t>
+    <t>00000000</t>
   </si>
   <si>
     <t>Alarm Enable Flags</t>
   </si>
   <si>
+    <t>0120</t>
+  </si>
+  <si>
     <t>Temperature High</t>
   </si>
   <si>
+    <t>0124</t>
+  </si>
+  <si>
     <t>Battery Charge Low</t>
   </si>
   <si>
+    <t>0126</t>
+  </si>
+  <si>
     <t>Battery Runtime Low</t>
   </si>
   <si>
+    <t>0128</t>
+  </si>
+  <si>
     <t>User System Name</t>
   </si>
   <si>
+    <t>01A0</t>
+  </si>
+  <si>
+    <t>534455204443205550532077697468</t>
+  </si>
+  <si>
     <t>User Device Name</t>
   </si>
   <si>
+    <t>01B0</t>
+  </si>
+  <si>
     <t>Battery Type</t>
   </si>
   <si>
+    <t>01CO</t>
+  </si>
+  <si>
     <t>Temperature Unit</t>
   </si>
   <si>
+    <t>01C2</t>
+  </si>
+  <si>
     <t>Configuration Flags</t>
   </si>
   <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>0000000000</t>
+  </si>
+  <si>
     <t>PC Shutdown_Enable/Disable</t>
   </si>
   <si>
+    <t>0225</t>
+  </si>
+  <si>
     <t>Scheduled Shutdown</t>
   </si>
   <si>
+    <t>0227</t>
+  </si>
+  <si>
+    <t>0000000000000000</t>
+  </si>
+  <si>
     <t>PC Shutdown Delay Count_Enable/Disable</t>
   </si>
   <si>
+    <t>022F</t>
+  </si>
+  <si>
     <t>Restart Period</t>
   </si>
   <si>
+    <t>0231</t>
+  </si>
+  <si>
     <t>Event Buffer Length</t>
   </si>
   <si>
+    <t>02A0</t>
+  </si>
+  <si>
     <t>Event Write Index</t>
   </si>
   <si>
+    <t>02A2</t>
+  </si>
+  <si>
     <t>Event Read Index</t>
   </si>
   <si>
+    <t>02A4</t>
+  </si>
+  <si>
     <t>Ambient Temp C.C 0</t>
   </si>
   <si>
+    <t>05E0</t>
+  </si>
+  <si>
     <t>Ambient Temp C.C 1</t>
   </si>
   <si>
+    <t>05E4</t>
+  </si>
+  <si>
     <t>BEM FET Temp C.C 0</t>
   </si>
   <si>
+    <t>0600</t>
+  </si>
+  <si>
     <t>BEM FET Temp C.C 1</t>
   </si>
   <si>
+    <t>0604</t>
+  </si>
+  <si>
     <t>Flyback TRF Temp C.C 0</t>
   </si>
   <si>
+    <t>0620</t>
+  </si>
+  <si>
     <t>Flyback TRF Temp C.C 1</t>
   </si>
   <si>
-    <t>0022</t>
-  </si>
-  <si>
-    <t>5344552032303234422D454950</t>
-  </si>
-  <si>
-    <t>0032</t>
-  </si>
-  <si>
-    <t>A9858001</t>
-  </si>
-  <si>
-    <t>003C</t>
-  </si>
-  <si>
-    <t>0046</t>
-  </si>
-  <si>
-    <t>0056</t>
-  </si>
-  <si>
-    <t>534455203230</t>
-  </si>
-  <si>
-    <t>0058</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>0124</t>
-  </si>
-  <si>
-    <t>0126</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>01A0</t>
-  </si>
-  <si>
-    <t>534455204443205550532077697468</t>
-  </si>
-  <si>
-    <t>01B0</t>
-  </si>
-  <si>
-    <t>01CO</t>
-  </si>
-  <si>
-    <t>01C2</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>0225</t>
-  </si>
-  <si>
-    <t>0227</t>
-  </si>
-  <si>
-    <t>022F</t>
-  </si>
-  <si>
-    <t>0231</t>
-  </si>
-  <si>
-    <t>02A0</t>
-  </si>
-  <si>
-    <t>02A2</t>
-  </si>
-  <si>
-    <t>02A4</t>
-  </si>
-  <si>
-    <t>05E0</t>
-  </si>
-  <si>
-    <t>05E4</t>
-  </si>
-  <si>
-    <t>0604</t>
-  </si>
-  <si>
-    <t>0620</t>
-  </si>
-  <si>
     <t>0624</t>
   </si>
   <si>
+    <t>Event Data 1</t>
+  </si>
+  <si>
     <t>02C0</t>
   </si>
   <si>
-    <t>0600</t>
-  </si>
-  <si>
-    <t>FF</t>
-  </si>
-  <si>
-    <t>=B36+0008</t>
-  </si>
-  <si>
-    <t>Event Data 1</t>
+    <t>FF00000000000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Display"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -295,7 +356,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,35 +364,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,7 +379,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -347,14 +387,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,22 +395,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,20 +410,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -411,175 +451,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -589,6 +642,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -614,7 +682,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,15 +717,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -673,17 +732,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -699,115 +752,142 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -856,7 +936,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -889,26 +969,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -941,23 +1004,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1119,24 +1165,19 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0906D4-3532-489F-B209-7EC47A9B24FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="36.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="103.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.625" customWidth="1"/>
+    <col min="2" max="2" width="25.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
     <col min="5" max="5" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1144,7 +1185,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1159,13 +1200,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D2">
         <v>128</v>
@@ -1173,13 +1214,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>128</v>
@@ -1187,13 +1228,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D4">
         <v>128</v>
@@ -1201,13 +1242,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
       </c>
       <c r="D5">
         <v>128</v>
@@ -1215,13 +1256,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>128</v>
@@ -1229,13 +1270,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>32</v>
@@ -1243,13 +1284,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -1257,13 +1298,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D9">
         <v>128</v>
@@ -1271,10 +1312,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>4141</v>
@@ -1285,13 +1326,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D11">
         <v>128</v>
@@ -1299,13 +1340,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D12">
         <v>128</v>
@@ -1313,13 +1354,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D13">
         <v>128</v>
@@ -1327,13 +1368,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D14">
         <v>128</v>
@@ -1341,13 +1382,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C15" s="2">
-        <v>32</v>
+        <v>3200</v>
       </c>
       <c r="D15">
         <v>128</v>
@@ -1355,13 +1396,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>1400</v>
       </c>
       <c r="D16">
         <v>128</v>
@@ -1369,13 +1410,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>54</v>
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C17" s="2">
-        <v>78</v>
+        <v>78000000</v>
       </c>
       <c r="D17">
         <v>128</v>
@@ -1383,13 +1424,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="D18">
         <v>128</v>
@@ -1397,13 +1438,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D19">
         <v>128</v>
@@ -1411,13 +1452,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D20">
         <v>128</v>
@@ -1425,13 +1466,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D21">
         <v>128</v>
@@ -1439,13 +1480,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="D22">
         <v>128</v>
@@ -1453,13 +1494,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D23">
         <v>128</v>
@@ -1467,13 +1508,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="D24">
         <v>128</v>
@@ -1481,13 +1522,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D25">
         <v>128</v>
@@ -1495,13 +1536,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="2">
-        <v>0</v>
+      <c r="C26" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D26">
         <v>128</v>
@@ -1509,13 +1550,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="2">
-        <v>0</v>
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D27">
         <v>128</v>
@@ -1523,13 +1564,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D28">
         <v>128</v>
@@ -1537,13 +1578,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D29">
         <v>128</v>
@@ -1551,13 +1592,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D30">
         <v>128</v>
@@ -1565,13 +1606,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="2">
-        <v>0</v>
       </c>
       <c r="D31">
         <v>128</v>
@@ -1579,13 +1620,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D32">
         <v>128</v>
@@ -1593,13 +1634,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="2">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D33">
         <v>128</v>
@@ -1607,13 +1648,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="2">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D34">
         <v>128</v>
@@ -1621,13 +1662,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D35">
         <v>128</v>
@@ -1635,32 +1676,27 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D36">
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="B37" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
     <row r="44" spans="1:4">
-      <c r="C44" s="3"/>
+      <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="C45" s="3"/>
+      <c r="C45" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
+++ b/PCBA/TesterSpecific/FRU PROGRAMMING TOOLKIT/Data/FRU Array.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="11580"/>
+    <workbookView windowWidth="28800" windowHeight="10980"/>
   </bookViews>
   <sheets>
     <sheet name="FRU Array" sheetId="1" r:id="rId1"/>
@@ -1172,7 +1172,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.625" customWidth="1"/>
     <col min="2" max="2" width="25.75" style="1" customWidth="1"/>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>128</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5">
